--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933193</v>
+        <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736</v>
+        <v>545031</v>
       </c>
       <c r="R2" t="n">
-        <v>7198995</v>
+        <v>7198840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933197</v>
+        <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>80226</v>
+        <v>79203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544719</v>
+        <v>544736</v>
       </c>
       <c r="R3" t="n">
-        <v>7199038</v>
+        <v>7198995</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>91800</v>
+        <v>80230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,12 +996,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
         <v>128934057</v>
       </c>
       <c r="B5" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>91914</v>
+        <v>91918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,22 +1214,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933927</v>
+        <v>128933206</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>91522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,37 +1237,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545139</v>
+        <v>544953</v>
       </c>
       <c r="R7" t="n">
-        <v>7198701</v>
+        <v>7198881</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,27 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933206</v>
+        <v>128933927</v>
       </c>
       <c r="B8" t="n">
-        <v>91518</v>
+        <v>79203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,41 +1348,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544953</v>
+        <v>545139</v>
       </c>
       <c r="R8" t="n">
-        <v>7198881</v>
+        <v>7198701</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,22 +1402,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,12 +1548,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
         <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,59 +1767,55 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933152</v>
+        <v>128934061</v>
       </c>
       <c r="B12" t="n">
-        <v>92201</v>
+        <v>80230</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545026</v>
+        <v>544855</v>
       </c>
       <c r="R12" t="n">
-        <v>7198767</v>
+        <v>7199022</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1848,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,12 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,60 +1869,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128934061</v>
+        <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>80226</v>
+        <v>92205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544855</v>
+        <v>545026</v>
       </c>
       <c r="R13" t="n">
-        <v>7199022</v>
+        <v>7198767</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1965,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,64 +1985,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B14" t="n">
-        <v>92078</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R14" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2077,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,60 +2097,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>92082</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R15" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
         <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
         <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933931</v>
+        <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>78877</v>
+        <v>91804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545235</v>
+        <v>545016</v>
       </c>
       <c r="R18" t="n">
-        <v>7198698</v>
+        <v>7198794</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2509,27 +2509,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,17 +2544,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934082</v>
+        <v>128934066</v>
       </c>
       <c r="B19" t="n">
-        <v>91800</v>
+        <v>80230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2591,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545016</v>
+        <v>544869</v>
       </c>
       <c r="R19" t="n">
-        <v>7198794</v>
+        <v>7198981</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2626,7 +2621,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2631,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,17 +2651,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128933931</v>
       </c>
       <c r="B20" t="n">
-        <v>80226</v>
+        <v>78881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>545235</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7198698</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2728,22 +2723,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
         <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,49 +2874,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933148</v>
+        <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>92082</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545231</v>
+        <v>544731</v>
       </c>
       <c r="R22" t="n">
-        <v>7198599</v>
+        <v>7198999</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,22 +2990,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933190</v>
+        <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,19 +3032,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544731</v>
+        <v>544710</v>
       </c>
       <c r="R23" t="n">
-        <v>7198999</v>
+        <v>7199001</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3081,12 +3089,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3095,50 +3098,51 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933194</v>
+        <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>92078</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3146,19 +3150,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544710</v>
+        <v>545231</v>
       </c>
       <c r="R24" t="n">
-        <v>7199001</v>
+        <v>7198599</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3201,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,19 +3210,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933195</v>
+        <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>80226</v>
+        <v>91804</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,41 +3453,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544710</v>
+        <v>545027</v>
       </c>
       <c r="R27" t="n">
-        <v>7199019</v>
+        <v>7198834</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3516,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,22 +3537,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B28" t="n">
-        <v>91800</v>
+        <v>80230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,37 +3560,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R28" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,12 +3648,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
         <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,14 +3760,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B30" t="n">
         <v>91522</v>
@@ -3778,44 +3778,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R30" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3844,7 +3837,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3854,7 +3847,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,29 +3856,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91518</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,37 +3885,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R31" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3952,7 +3951,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3961,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,18 +3970,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3992,7 +3992,7 @@
         <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4099,7 +4099,7 @@
         <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4413,12 +4413,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
         <v>128933200</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4524,12 +4524,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4539,7 +4539,7 @@
         <v>128933146</v>
       </c>
       <c r="B37" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4640,12 +4640,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4655,7 +4655,7 @@
         <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,39 +4757,39 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934059</v>
+        <v>128934063</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544753</v>
+        <v>544870</v>
       </c>
       <c r="R39" t="n">
-        <v>7199025</v>
+        <v>7198981</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gammla ringhack på gran</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,39 +4869,39 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933144</v>
+        <v>128933185</v>
       </c>
       <c r="B40" t="n">
-        <v>80253</v>
+        <v>80230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545205</v>
+        <v>544719</v>
       </c>
       <c r="R40" t="n">
-        <v>7198721</v>
+        <v>7198950</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4945,22 +4945,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4975,12 +4975,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
         <v>128934018</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,39 +5087,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933185</v>
+        <v>128933144</v>
       </c>
       <c r="B42" t="n">
-        <v>80226</v>
+        <v>80257</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544719</v>
+        <v>545205</v>
       </c>
       <c r="R42" t="n">
-        <v>7198950</v>
+        <v>7198721</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5163,22 +5163,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,44 +5193,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934063</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>91914</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544870</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198981</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal låga av tall</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5416,12 +5416,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,59 +5528,55 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933207</v>
+        <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>80226</v>
+        <v>92082</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544978</v>
+        <v>544728</v>
       </c>
       <c r="R46" t="n">
-        <v>7198868</v>
+        <v>7198999</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5609,7 +5605,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5619,7 +5615,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5634,60 +5635,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128934028</v>
+        <v>128933207</v>
       </c>
       <c r="B47" t="n">
-        <v>92078</v>
+        <v>80230</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544728</v>
+        <v>544978</v>
       </c>
       <c r="R47" t="n">
-        <v>7198999</v>
+        <v>7198868</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5716,7 +5721,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5726,12 +5731,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5746,12 +5746,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>79203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R2" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933193</v>
+        <v>128933210</v>
       </c>
       <c r="B3" t="n">
-        <v>79203</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544736</v>
+        <v>545031</v>
       </c>
       <c r="R3" t="n">
-        <v>7198995</v>
+        <v>7198840</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933206</v>
+        <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>91522</v>
+        <v>79203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,41 +1237,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544953</v>
+        <v>545139</v>
       </c>
       <c r="R7" t="n">
-        <v>7198881</v>
+        <v>7198701</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1291,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1326,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933927</v>
+        <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>79203</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,37 +1349,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545139</v>
+        <v>544953</v>
       </c>
       <c r="R8" t="n">
-        <v>7198701</v>
+        <v>7198881</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,27 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1997,48 +1997,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>92082</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R14" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,64 +2101,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>92082</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R15" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934066</v>
+        <v>128933199</v>
       </c>
       <c r="B19" t="n">
-        <v>80230</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,37 +2562,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544869</v>
+        <v>544762</v>
       </c>
       <c r="R19" t="n">
-        <v>7198981</v>
+        <v>7199027</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2621,7 +2630,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2631,7 +2640,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,22 +2655,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933931</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>78881</v>
+        <v>80230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545235</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7198698</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2723,27 +2732,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128933931</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2785,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>545235</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198698</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,22 +2839,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B27" t="n">
-        <v>91804</v>
+        <v>80230</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,37 +3453,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R27" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,19 +3541,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933195</v>
+        <v>128934023</v>
       </c>
       <c r="B28" t="n">
         <v>80230</v>
@@ -3577,21 +3581,17 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544710</v>
+        <v>544764</v>
       </c>
       <c r="R28" t="n">
-        <v>7199019</v>
+        <v>7198968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>80230</v>
+        <v>91804</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R29" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R36" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,22 +4494,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4536,10 +4541,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,21 +4552,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4575,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R37" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4605,27 +4610,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,48 +4652,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934043</v>
+        <v>128933185</v>
       </c>
       <c r="B38" t="n">
-        <v>92082</v>
+        <v>80230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544738</v>
+        <v>544719</v>
       </c>
       <c r="R38" t="n">
-        <v>7199019</v>
+        <v>7198950</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,12 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,44 +4751,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934063</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>92082</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4799,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544870</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198981</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4834,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,12 +4843,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal låga av tall</t>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,32 +4875,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933185</v>
+        <v>128933144</v>
       </c>
       <c r="B40" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4915,10 +4914,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544719</v>
+        <v>545205</v>
       </c>
       <c r="R40" t="n">
-        <v>7198950</v>
+        <v>7198721</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4945,22 +4944,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5094,10 +5093,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933144</v>
+        <v>128934063</v>
       </c>
       <c r="B42" t="n">
-        <v>80257</v>
+        <v>91918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,41 +5104,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545205</v>
+        <v>544870</v>
       </c>
       <c r="R42" t="n">
-        <v>7198721</v>
+        <v>7198981</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5163,22 +5158,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,12 +5193,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933193</v>
+        <v>128933197</v>
       </c>
       <c r="B2" t="n">
-        <v>79203</v>
+        <v>80230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736</v>
+        <v>544719</v>
       </c>
       <c r="R2" t="n">
-        <v>7198995</v>
+        <v>7199038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>91804</v>
+        <v>79203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R3" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80230</v>
+        <v>91804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>80230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,46 +2562,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R19" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,7 +2621,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2640,7 +2631,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,22 +2646,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128933931</v>
       </c>
       <c r="B20" t="n">
-        <v>80230</v>
+        <v>78881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>545235</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7198698</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2732,22 +2723,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2774,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,27 +2844,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933195</v>
+        <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>80230</v>
+        <v>91804</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,41 +3453,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544710</v>
+        <v>545027</v>
       </c>
       <c r="R27" t="n">
-        <v>7199019</v>
+        <v>7198834</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3516,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,19 +3537,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934023</v>
+        <v>128933195</v>
       </c>
       <c r="B28" t="n">
         <v>80230</v>
@@ -3581,17 +3577,21 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544764</v>
+        <v>544710</v>
       </c>
       <c r="R28" t="n">
-        <v>7198968</v>
+        <v>7199019</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934080</v>
+        <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>91804</v>
+        <v>80230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545027</v>
+        <v>544764</v>
       </c>
       <c r="R29" t="n">
-        <v>7198834</v>
+        <v>7198968</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,37 +3778,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R30" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,7 +3844,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3847,7 +3854,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,28 +3863,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,44 +3893,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R31" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3951,7 +3952,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3961,7 +3962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,29 +3971,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79203</v>
+        <v>80230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,37 +4000,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4073,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4088,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80230</v>
+        <v>79203</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,41 +4111,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4652,52 +4652,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933185</v>
+        <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>80230</v>
+        <v>92082</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544719</v>
+        <v>544738</v>
       </c>
       <c r="R38" t="n">
-        <v>7198950</v>
+        <v>7199019</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4726,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4732,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,60 +4752,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934043</v>
+        <v>128933185</v>
       </c>
       <c r="B39" t="n">
-        <v>92082</v>
+        <v>80230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544738</v>
+        <v>544719</v>
       </c>
       <c r="R39" t="n">
-        <v>7199019</v>
+        <v>7198950</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4833,7 +4838,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,12 +4848,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,61 +4863,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933144</v>
+        <v>128934018</v>
       </c>
       <c r="B40" t="n">
-        <v>80257</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545205</v>
+        <v>544728</v>
       </c>
       <c r="R40" t="n">
-        <v>7198721</v>
+        <v>7198926</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4944,22 +4940,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,57 +4970,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934018</v>
+        <v>128933144</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>80257</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544728</v>
+        <v>545205</v>
       </c>
       <c r="R41" t="n">
-        <v>7198926</v>
+        <v>7198721</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5051,22 +5051,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,44 +5081,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934063</v>
+        <v>128934059</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544870</v>
+        <v>544753</v>
       </c>
       <c r="R42" t="n">
-        <v>7198981</v>
+        <v>7199025</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal låga av tall</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5205,32 +5205,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934059</v>
+        <v>128934063</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544753</v>
+        <v>544870</v>
       </c>
       <c r="R43" t="n">
-        <v>7199025</v>
+        <v>7198981</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gammla ringhack på gran</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>80230</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R2" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
         <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>91804</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>128934057</v>
       </c>
       <c r="B5" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>128934061</v>
       </c>
       <c r="B12" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934066</v>
+        <v>128933199</v>
       </c>
       <c r="B19" t="n">
-        <v>80230</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,37 +2562,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544869</v>
+        <v>544762</v>
       </c>
       <c r="R19" t="n">
-        <v>7198981</v>
+        <v>7199027</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2621,7 +2630,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2631,7 +2640,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,22 +2655,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933931</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>78881</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545235</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7198698</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2723,27 +2732,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128933931</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>78786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2785,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>545235</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198698</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,22 +2839,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B27" t="n">
-        <v>91804</v>
+        <v>80135</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,37 +3453,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R27" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,22 +3541,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933195</v>
+        <v>128934023</v>
       </c>
       <c r="B28" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3581,17 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544710</v>
+        <v>544764</v>
       </c>
       <c r="R28" t="n">
-        <v>7199019</v>
+        <v>7198968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>80230</v>
+        <v>91809</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R29" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>91527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,44 +3778,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R30" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3844,7 +3837,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3854,7 +3847,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,29 +3856,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>91531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,37 +3885,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R31" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3952,7 +3951,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3961,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,28 +3970,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80230</v>
+        <v>79108</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,41 +4000,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4073,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79203</v>
+        <v>80135</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4111,37 +4107,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B36" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R36" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,27 +4494,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4541,10 +4536,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,21 +4547,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4580,10 +4575,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R37" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4610,22 +4605,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,48 +4652,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934043</v>
+        <v>128933185</v>
       </c>
       <c r="B38" t="n">
-        <v>92082</v>
+        <v>80135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544738</v>
+        <v>544719</v>
       </c>
       <c r="R38" t="n">
-        <v>7199019</v>
+        <v>7198950</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,12 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,64 +4751,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933185</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>80230</v>
+        <v>92087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544719</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198950</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4838,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4848,7 +4843,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,44 +4863,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934018</v>
+        <v>128934063</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>91923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544728</v>
+        <v>544870</v>
       </c>
       <c r="R40" t="n">
-        <v>7198926</v>
+        <v>7198981</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,7 +4955,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4982,49 +4987,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933144</v>
+        <v>128934018</v>
       </c>
       <c r="B41" t="n">
-        <v>80257</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545205</v>
+        <v>544728</v>
       </c>
       <c r="R41" t="n">
-        <v>7198721</v>
+        <v>7198926</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5051,22 +5052,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,60 +5082,64 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934059</v>
+        <v>128933144</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>80162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544753</v>
+        <v>545205</v>
       </c>
       <c r="R42" t="n">
-        <v>7199025</v>
+        <v>7198721</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5158,27 +5163,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,44 +5193,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934063</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544870</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198981</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal låga av tall</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5320,7 +5320,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>128933207</v>
       </c>
       <c r="B47" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -2886,37 +2886,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933148</v>
+        <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>92095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545231</v>
+        <v>544731</v>
       </c>
       <c r="R22" t="n">
-        <v>7198599</v>
+        <v>7198999</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,7 +3002,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933190</v>
+        <v>128933194</v>
       </c>
       <c r="B23" t="n">
         <v>92095</v>
@@ -3027,19 +3032,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544731</v>
+        <v>544710</v>
       </c>
       <c r="R23" t="n">
-        <v>7198999</v>
+        <v>7199001</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3081,12 +3089,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3095,6 +3098,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3106,39 +3110,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933194</v>
+        <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>92095</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3146,19 +3150,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544710</v>
+        <v>545231</v>
       </c>
       <c r="R24" t="n">
-        <v>7199001</v>
+        <v>7198599</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3201,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,7 +3210,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B30" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,37 +3778,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R30" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,7 +3844,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3847,7 +3854,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,28 +3863,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B31" t="n">
-        <v>91538</v>
+        <v>91534</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,44 +3893,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R31" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3951,7 +3952,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3961,7 +3962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,29 +3971,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79113</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,37 +4000,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4073,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4088,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>79113</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,41 +4111,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128933210</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933203</v>
+        <v>128934048</v>
       </c>
       <c r="B9" t="n">
         <v>80140</v>
@@ -1477,24 +1477,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544919</v>
+        <v>544735</v>
       </c>
       <c r="R9" t="n">
-        <v>7198905</v>
+        <v>7199043</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,19 +1544,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934048</v>
+        <v>128933203</v>
       </c>
       <c r="B10" t="n">
         <v>80140</v>
@@ -1588,20 +1584,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544735</v>
+        <v>544919</v>
       </c>
       <c r="R10" t="n">
-        <v>7199043</v>
+        <v>7198905</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,12 +1655,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1767,59 +1767,55 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933152</v>
+        <v>128934061</v>
       </c>
       <c r="B12" t="n">
-        <v>92218</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545026</v>
+        <v>544855</v>
       </c>
       <c r="R12" t="n">
-        <v>7198767</v>
+        <v>7199022</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1848,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,12 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,60 +1869,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128934061</v>
+        <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>92223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544855</v>
+        <v>545026</v>
       </c>
       <c r="R13" t="n">
-        <v>7199022</v>
+        <v>7198767</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1965,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,12 +1985,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934030</v>
+        <v>128934070</v>
       </c>
       <c r="B16" t="n">
         <v>80140</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544731</v>
+        <v>544967</v>
       </c>
       <c r="R16" t="n">
-        <v>7198998</v>
+        <v>7198870</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,12 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,14 +2325,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934070</v>
+        <v>128934030</v>
       </c>
       <c r="B17" t="n">
         <v>80140</v>
@@ -2372,13 +2367,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544967</v>
+        <v>544731</v>
       </c>
       <c r="R17" t="n">
-        <v>7198870</v>
+        <v>7198998</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,7 +2402,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2412,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934082</v>
+        <v>128933199</v>
       </c>
       <c r="B18" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,37 +2455,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545016</v>
+        <v>544762</v>
       </c>
       <c r="R18" t="n">
-        <v>7198794</v>
+        <v>7199027</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2514,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,22 +2548,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>91808</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2571,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2595,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R19" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2621,7 +2630,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2631,7 +2640,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,17 +2660,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,46 +2678,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,12 +2762,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
         <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3760,17 +3760,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91538</v>
+        <v>91537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,44 +3778,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R30" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3844,7 +3837,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3854,7 +3847,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,29 +3856,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91534</v>
+        <v>91541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,37 +3885,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R31" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3952,7 +3951,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3961,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,28 +3970,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>79113</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,41 +4000,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4073,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79113</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4111,37 +4107,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R36" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,22 +4494,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4536,10 +4541,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,21 +4552,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4575,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R37" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4605,27 +4610,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4655,7 +4655,7 @@
         <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934059</v>
+        <v>128934063</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>91934</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544753</v>
+        <v>544870</v>
       </c>
       <c r="R40" t="n">
-        <v>7199025</v>
+        <v>7198981</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gammla ringhack på gran</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5087,17 +5087,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934063</v>
+        <v>128933144</v>
       </c>
       <c r="B42" t="n">
-        <v>91931</v>
+        <v>80167</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,37 +5105,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544870</v>
+        <v>545205</v>
       </c>
       <c r="R42" t="n">
-        <v>7198981</v>
+        <v>7198721</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5159,27 +5163,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5194,64 +5193,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933144</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>80167</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545205</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198721</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5275,22 +5270,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,12 +5305,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5538,7 +5538,7 @@
         <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933193</v>
+        <v>128933197</v>
       </c>
       <c r="B2" t="n">
-        <v>79113</v>
+        <v>80141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736</v>
+        <v>544719</v>
       </c>
       <c r="R2" t="n">
-        <v>7198995</v>
+        <v>7199038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>91808</v>
+        <v>79114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R3" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>128934057</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>79113</v>
+        <v>79114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934048</v>
+        <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,20 +1477,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544735</v>
+        <v>544919</v>
       </c>
       <c r="R9" t="n">
-        <v>7199043</v>
+        <v>7198905</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128933203</v>
+        <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,24 +1588,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544919</v>
+        <v>544735</v>
       </c>
       <c r="R10" t="n">
-        <v>7198905</v>
+        <v>7199043</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,60 +1655,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128934052</v>
+        <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>92226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544774</v>
+        <v>545026</v>
       </c>
       <c r="R11" t="n">
-        <v>7199045</v>
+        <v>7198767</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,22 +1771,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934061</v>
+        <v>128934052</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,13 +1818,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544855</v>
+        <v>544774</v>
       </c>
       <c r="R12" t="n">
-        <v>7199022</v>
+        <v>7199045</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,59 +1883,55 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933152</v>
+        <v>128934061</v>
       </c>
       <c r="B13" t="n">
-        <v>92223</v>
+        <v>80141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545026</v>
+        <v>544855</v>
       </c>
       <c r="R13" t="n">
-        <v>7198767</v>
+        <v>7199022</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,12 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,64 +1985,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B14" t="n">
-        <v>92100</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R14" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2077,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,60 +2097,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>92103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R15" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,22 +2213,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934070</v>
+        <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544967</v>
+        <v>544731</v>
       </c>
       <c r="R16" t="n">
-        <v>7198870</v>
+        <v>7198998</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,17 +2330,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934030</v>
+        <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,13 +2372,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544731</v>
+        <v>544967</v>
       </c>
       <c r="R17" t="n">
-        <v>7198998</v>
+        <v>7198870</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2412,12 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933199</v>
+        <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,46 +2455,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544762</v>
+        <v>545016</v>
       </c>
       <c r="R18" t="n">
-        <v>7199027</v>
+        <v>7198794</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2523,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,22 +2539,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934082</v>
+        <v>128934066</v>
       </c>
       <c r="B19" t="n">
-        <v>91808</v>
+        <v>80141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2595,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545016</v>
+        <v>544869</v>
       </c>
       <c r="R19" t="n">
-        <v>7198794</v>
+        <v>7198981</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2630,7 +2621,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2640,7 +2631,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,17 +2651,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128933931</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>545235</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7198698</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2732,22 +2723,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,17 +2763,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,27 +2844,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
         <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
         <v>128933195</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
         <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3877,7 +3877,7 @@
         <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79113</v>
+        <v>80141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,37 +4000,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4073,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4088,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>79114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,41 +4111,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4317,7 +4317,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4767,7 +4767,7 @@
         <v>128933185</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934063</v>
+        <v>128934018</v>
       </c>
       <c r="B40" t="n">
-        <v>91934</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544870</v>
+        <v>544728</v>
       </c>
       <c r="R40" t="n">
-        <v>7198981</v>
+        <v>7198926</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,12 +4955,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4980,39 +4975,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934018</v>
+        <v>128934063</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>91937</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5022,13 +5017,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544728</v>
+        <v>544870</v>
       </c>
       <c r="R41" t="n">
-        <v>7198926</v>
+        <v>7198981</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5057,7 +5052,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5067,7 +5062,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5097,7 +5097,7 @@
         <v>128933144</v>
       </c>
       <c r="B42" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5538,7 +5538,7 @@
         <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5650,7 +5650,7 @@
         <v>128933207</v>
       </c>
       <c r="B47" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>80141</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R2" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>91811</v>
+        <v>80141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1997,48 +1997,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>92103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R14" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,64 +2101,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>92103</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R15" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3002,32 +3002,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933194</v>
+        <v>128933148</v>
       </c>
       <c r="B23" t="n">
-        <v>92103</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3035,19 +3035,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544710</v>
+        <v>545231</v>
       </c>
       <c r="R23" t="n">
-        <v>7199001</v>
+        <v>7198599</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3079,7 +3076,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,7 +3086,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,7 +3095,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3110,39 +3106,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933148</v>
+        <v>128933194</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>92103</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3150,16 +3146,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545231</v>
+        <v>544710</v>
       </c>
       <c r="R24" t="n">
-        <v>7198599</v>
+        <v>7199001</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3191,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3201,7 +3200,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3210,6 +3209,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80141</v>
+        <v>79114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,41 +4000,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4073,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79114</v>
+        <v>80141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4111,37 +4107,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B36" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R36" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,27 +4494,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4541,10 +4536,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,21 +4547,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4580,10 +4575,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R37" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4610,22 +4605,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,48 +4652,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934043</v>
+        <v>128933144</v>
       </c>
       <c r="B38" t="n">
-        <v>92103</v>
+        <v>80168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544738</v>
+        <v>545205</v>
       </c>
       <c r="R38" t="n">
-        <v>7199019</v>
+        <v>7198721</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4717,27 +4721,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,64 +4751,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933185</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>80141</v>
+        <v>92103</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544719</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198950</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4838,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4848,7 +4843,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,22 +4863,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934018</v>
+        <v>128933185</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4886,34 +4886,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544728</v>
+        <v>544719</v>
       </c>
       <c r="R40" t="n">
-        <v>7198926</v>
+        <v>7198950</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,7 +4959,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4970,44 +4974,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934063</v>
+        <v>128934018</v>
       </c>
       <c r="B41" t="n">
-        <v>91937</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5017,13 +5021,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544870</v>
+        <v>544728</v>
       </c>
       <c r="R41" t="n">
-        <v>7198981</v>
+        <v>7198926</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5052,7 +5056,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5062,12 +5066,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5094,10 +5093,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933144</v>
+        <v>128934063</v>
       </c>
       <c r="B42" t="n">
-        <v>80168</v>
+        <v>91937</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,41 +5104,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545205</v>
+        <v>544870</v>
       </c>
       <c r="R42" t="n">
-        <v>7198721</v>
+        <v>7198981</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5163,22 +5158,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,12 +5193,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>80141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R2" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80141</v>
+        <v>91811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,48 +1008,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>80141</v>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R5" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,64 +1107,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>80141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R6" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933203</v>
+        <v>128934048</v>
       </c>
       <c r="B9" t="n">
         <v>80141</v>
@@ -1477,24 +1477,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544919</v>
+        <v>544735</v>
       </c>
       <c r="R9" t="n">
-        <v>7198905</v>
+        <v>7199043</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,19 +1544,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934048</v>
+        <v>128933203</v>
       </c>
       <c r="B10" t="n">
         <v>80141</v>
@@ -1588,20 +1584,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544735</v>
+        <v>544919</v>
       </c>
       <c r="R10" t="n">
-        <v>7199043</v>
+        <v>7198905</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,12 +1655,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934030</v>
+        <v>128934070</v>
       </c>
       <c r="B16" t="n">
         <v>80141</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544731</v>
+        <v>544967</v>
       </c>
       <c r="R16" t="n">
-        <v>7198998</v>
+        <v>7198870</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,12 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2332,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934070</v>
+        <v>128934030</v>
       </c>
       <c r="B17" t="n">
         <v>80141</v>
@@ -2372,13 +2367,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544967</v>
+        <v>544731</v>
       </c>
       <c r="R17" t="n">
-        <v>7198870</v>
+        <v>7198998</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,7 +2402,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2412,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934082</v>
+        <v>128933931</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545016</v>
+        <v>545235</v>
       </c>
       <c r="R18" t="n">
-        <v>7198794</v>
+        <v>7198698</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2509,22 +2509,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B19" t="n">
-        <v>80141</v>
+        <v>91811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R19" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2621,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2631,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,37 +2674,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R20" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,27 +2737,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,22 +2767,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2790,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,19 +2874,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933190</v>
+        <v>128933194</v>
       </c>
       <c r="B22" t="n">
         <v>92103</v>
@@ -2916,19 +2916,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544731</v>
+        <v>544710</v>
       </c>
       <c r="R22" t="n">
-        <v>7198999</v>
+        <v>7199001</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2963,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,12 +2973,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,6 +2982,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2995,44 +2994,44 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933148</v>
+        <v>128933190</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>92103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3041,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545231</v>
+        <v>544731</v>
       </c>
       <c r="R23" t="n">
-        <v>7198599</v>
+        <v>7198999</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3076,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3086,7 +3085,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,32 +3117,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933194</v>
+        <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>92103</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3146,19 +3150,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544710</v>
+        <v>545231</v>
       </c>
       <c r="R24" t="n">
-        <v>7199001</v>
+        <v>7198599</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3201,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,7 +3210,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B27" t="n">
-        <v>91811</v>
+        <v>80141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,37 +3453,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R27" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,19 +3541,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933195</v>
+        <v>128934023</v>
       </c>
       <c r="B28" t="n">
         <v>80141</v>
@@ -3577,21 +3581,17 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544710</v>
+        <v>544764</v>
       </c>
       <c r="R28" t="n">
-        <v>7199019</v>
+        <v>7198968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>80141</v>
+        <v>91811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R29" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R36" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,22 +4494,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4536,10 +4541,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,21 +4552,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4575,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R37" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4605,27 +4610,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,32 +4652,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933144</v>
+        <v>128933185</v>
       </c>
       <c r="B38" t="n">
-        <v>80168</v>
+        <v>80141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545205</v>
+        <v>544719</v>
       </c>
       <c r="R38" t="n">
-        <v>7198721</v>
+        <v>7198950</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4721,22 +4721,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4875,52 +4875,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933185</v>
+        <v>128934063</v>
       </c>
       <c r="B40" t="n">
-        <v>80141</v>
+        <v>91937</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544719</v>
+        <v>544870</v>
       </c>
       <c r="R40" t="n">
-        <v>7198950</v>
+        <v>7198981</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4949,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,7 +4955,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,22 +4975,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934018</v>
+        <v>128934059</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4997,21 +4998,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,13 +5022,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544728</v>
+        <v>544753</v>
       </c>
       <c r="R41" t="n">
-        <v>7198926</v>
+        <v>7199025</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5056,7 +5057,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,7 +5067,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,10 +5099,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934063</v>
+        <v>128933144</v>
       </c>
       <c r="B42" t="n">
-        <v>91937</v>
+        <v>80168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5104,37 +5110,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544870</v>
+        <v>545205</v>
       </c>
       <c r="R42" t="n">
-        <v>7198981</v>
+        <v>7198721</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5158,27 +5168,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,22 +5198,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934059</v>
+        <v>128934018</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5216,21 +5221,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5240,13 +5245,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544753</v>
+        <v>544728</v>
       </c>
       <c r="R43" t="n">
-        <v>7199025</v>
+        <v>7198926</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5275,7 +5280,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5290,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5535,48 +5535,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128934028</v>
+        <v>128933207</v>
       </c>
       <c r="B46" t="n">
-        <v>92103</v>
+        <v>80141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544728</v>
+        <v>544978</v>
       </c>
       <c r="R46" t="n">
-        <v>7198999</v>
+        <v>7198868</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5605,7 +5609,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5615,12 +5619,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5635,64 +5634,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933207</v>
+        <v>128934028</v>
       </c>
       <c r="B47" t="n">
-        <v>80141</v>
+        <v>92103</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544978</v>
+        <v>544728</v>
       </c>
       <c r="R47" t="n">
-        <v>7198868</v>
+        <v>7198999</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5721,7 +5716,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5731,7 +5726,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5746,12 +5746,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>80141</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R2" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
         <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>79114</v>
+        <v>79118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>91811</v>
+        <v>80145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>79114</v>
+        <v>79118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934048</v>
+        <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,20 +1477,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544735</v>
+        <v>544919</v>
       </c>
       <c r="R9" t="n">
-        <v>7199043</v>
+        <v>7198905</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128933203</v>
+        <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,24 +1588,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544919</v>
+        <v>544735</v>
       </c>
       <c r="R10" t="n">
-        <v>7198905</v>
+        <v>7199043</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,12 +1655,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128934052</v>
       </c>
       <c r="B12" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>128934061</v>
       </c>
       <c r="B13" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934070</v>
+        <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544967</v>
+        <v>544731</v>
       </c>
       <c r="R16" t="n">
-        <v>7198870</v>
+        <v>7198998</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934030</v>
+        <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,13 +2372,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544731</v>
+        <v>544967</v>
       </c>
       <c r="R17" t="n">
-        <v>7198998</v>
+        <v>7198870</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2412,12 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,7 +2447,7 @@
         <v>128933931</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>128934082</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,46 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2742,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2752,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,22 +2758,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934066</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544869</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198981</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,22 +2874,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933194</v>
+        <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2916,22 +2916,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544710</v>
+        <v>544731</v>
       </c>
       <c r="R22" t="n">
-        <v>7199001</v>
+        <v>7198999</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2963,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2973,7 +2970,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,7 +2984,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2994,17 +2995,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933190</v>
+        <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,19 +3032,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544731</v>
+        <v>544710</v>
       </c>
       <c r="R23" t="n">
-        <v>7198999</v>
+        <v>7199001</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3075,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,12 +3089,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,6 +3098,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
         <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128933195</v>
       </c>
       <c r="B27" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B28" t="n">
-        <v>80141</v>
+        <v>91818</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R28" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934080</v>
+        <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>91811</v>
+        <v>80145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545027</v>
+        <v>544764</v>
       </c>
       <c r="R29" t="n">
-        <v>7198834</v>
+        <v>7198968</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91551</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,37 +3778,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R30" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,7 +3844,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3847,7 +3854,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,28 +3863,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B31" t="n">
-        <v>91544</v>
+        <v>91547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,44 +3893,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R31" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3951,7 +3952,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3961,7 +3962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,29 +3971,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79114</v>
+        <v>80145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,37 +4000,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4073,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4088,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80141</v>
+        <v>79118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,41 +4111,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B36" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R36" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,27 +4494,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4541,10 +4536,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,21 +4547,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4580,10 +4575,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R37" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4610,22 +4605,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,10 +4652,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933185</v>
+        <v>128934059</v>
       </c>
       <c r="B38" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4663,41 +4663,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544719</v>
+        <v>544753</v>
       </c>
       <c r="R38" t="n">
-        <v>7198950</v>
+        <v>7199025</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4726,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4732,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,60 +4752,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934043</v>
+        <v>128933144</v>
       </c>
       <c r="B39" t="n">
-        <v>92103</v>
+        <v>80172</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544738</v>
+        <v>545205</v>
       </c>
       <c r="R39" t="n">
-        <v>7199019</v>
+        <v>7198721</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,27 +4833,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,12 +4863,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4878,7 +4878,7 @@
         <v>128934063</v>
       </c>
       <c r="B40" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,32 +4987,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934059</v>
+        <v>128934043</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>92110</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544753</v>
+        <v>544738</v>
       </c>
       <c r="R41" t="n">
-        <v>7199025</v>
+        <v>7199019</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gammla ringhack på gran</t>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5099,49 +5099,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933144</v>
+        <v>128934018</v>
       </c>
       <c r="B42" t="n">
-        <v>80168</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545205</v>
+        <v>544728</v>
       </c>
       <c r="R42" t="n">
-        <v>7198721</v>
+        <v>7198926</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5168,22 +5164,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5198,22 +5194,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934018</v>
+        <v>128933185</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>80145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5221,34 +5217,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544728</v>
+        <v>544719</v>
       </c>
       <c r="R43" t="n">
-        <v>7198926</v>
+        <v>7198950</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,12 +5305,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128933207</v>
       </c>
       <c r="B46" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>128934028</v>
       </c>
       <c r="B47" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -1008,52 +1008,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B5" t="n">
-        <v>91944</v>
+        <v>80145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R5" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,60 +1103,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>80145</v>
+        <v>91944</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R6" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1997,52 +1997,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B14" t="n">
-        <v>92110</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R14" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2077,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,60 +2097,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>92110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R15" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934082</v>
+        <v>128933199</v>
       </c>
       <c r="B19" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,37 +2567,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545016</v>
+        <v>544762</v>
       </c>
       <c r="R19" t="n">
-        <v>7198794</v>
+        <v>7199027</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2635,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2645,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,22 +2660,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>91818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2733,7 +2742,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2752,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2790,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91551</v>
+        <v>91547</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,44 +3778,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R30" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3844,7 +3837,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3854,7 +3847,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,29 +3856,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91547</v>
+        <v>91551</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,37 +3885,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R31" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3952,7 +3951,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3961,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,28 +3970,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80145</v>
+        <v>79118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,41 +4000,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4073,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79118</v>
+        <v>80145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4111,37 +4107,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4652,48 +4652,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934059</v>
+        <v>128933144</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>80172</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544753</v>
+        <v>545205</v>
       </c>
       <c r="R38" t="n">
-        <v>7199025</v>
+        <v>7198721</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4717,27 +4721,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,64 +4751,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933144</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>80172</v>
+        <v>92110</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545205</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198721</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4833,22 +4828,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,60 +4863,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934063</v>
+        <v>128933185</v>
       </c>
       <c r="B40" t="n">
-        <v>91944</v>
+        <v>80145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544870</v>
+        <v>544719</v>
       </c>
       <c r="R40" t="n">
-        <v>7198981</v>
+        <v>7198950</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,12 +4959,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4975,44 +4974,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934043</v>
+        <v>128934059</v>
       </c>
       <c r="B41" t="n">
-        <v>92110</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5022,10 +5021,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544738</v>
+        <v>544753</v>
       </c>
       <c r="R41" t="n">
-        <v>7199019</v>
+        <v>7199025</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5057,7 +5056,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5067,12 +5066,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Högt upp gammal sälg</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5099,32 +5098,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934018</v>
+        <v>128934063</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>91944</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5134,13 +5133,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544728</v>
+        <v>544870</v>
       </c>
       <c r="R42" t="n">
-        <v>7198926</v>
+        <v>7198981</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5169,7 +5168,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5179,7 +5178,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5206,10 +5210,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933185</v>
+        <v>128934018</v>
       </c>
       <c r="B43" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5217,38 +5221,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544719</v>
+        <v>544728</v>
       </c>
       <c r="R43" t="n">
-        <v>7198950</v>
+        <v>7198926</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,12 +5305,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,48 +1008,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>80145</v>
+        <v>91951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R5" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,64 +1107,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>91944</v>
+        <v>80145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R6" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1667,52 +1667,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933152</v>
+        <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>80145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545026</v>
+        <v>544774</v>
       </c>
       <c r="R11" t="n">
-        <v>7198767</v>
+        <v>7199045</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,19 +1762,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934052</v>
+        <v>128934061</v>
       </c>
       <c r="B12" t="n">
         <v>80145</v>
@@ -1818,13 +1809,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544774</v>
+        <v>544855</v>
       </c>
       <c r="R12" t="n">
-        <v>7199045</v>
+        <v>7199022</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,48 +1881,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128934061</v>
+        <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>92240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544855</v>
+        <v>545026</v>
       </c>
       <c r="R13" t="n">
-        <v>7199022</v>
+        <v>7198767</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1965,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,60 +1985,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R14" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,64 +2101,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>92110</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R15" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933931</v>
+        <v>128934066</v>
       </c>
       <c r="B18" t="n">
-        <v>78796</v>
+        <v>80145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545235</v>
+        <v>544869</v>
       </c>
       <c r="R18" t="n">
-        <v>7198698</v>
+        <v>7198981</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2509,27 +2509,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933199</v>
+        <v>128933931</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,46 +2562,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544762</v>
+        <v>545235</v>
       </c>
       <c r="R19" t="n">
-        <v>7199027</v>
+        <v>7198698</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,22 +2616,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,12 +2651,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2675,7 +2666,7 @@
         <v>128934082</v>
       </c>
       <c r="B20" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934066</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544869</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198981</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,49 +2874,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933190</v>
+        <v>128933148</v>
       </c>
       <c r="B22" t="n">
-        <v>92110</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544731</v>
+        <v>545231</v>
       </c>
       <c r="R22" t="n">
-        <v>7198999</v>
+        <v>7198599</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,12 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,10 +2997,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933194</v>
+        <v>128933190</v>
       </c>
       <c r="B23" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,22 +3027,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544710</v>
+        <v>544731</v>
       </c>
       <c r="R23" t="n">
-        <v>7199001</v>
+        <v>7198999</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3079,7 +3071,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,7 +3081,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,7 +3095,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3110,39 +3106,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933148</v>
+        <v>128933194</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>92117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3150,16 +3146,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545231</v>
+        <v>544710</v>
       </c>
       <c r="R24" t="n">
-        <v>7198599</v>
+        <v>7199001</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3191,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3201,7 +3200,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3210,6 +3209,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933195</v>
+        <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>91825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,41 +3453,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544710</v>
+        <v>545027</v>
       </c>
       <c r="R27" t="n">
-        <v>7199019</v>
+        <v>7198834</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3516,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,22 +3537,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B28" t="n">
-        <v>91818</v>
+        <v>80145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,37 +3560,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R28" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,12 +3648,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
         <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4652,52 +4652,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933144</v>
+        <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>80172</v>
+        <v>92117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545205</v>
+        <v>544738</v>
       </c>
       <c r="R38" t="n">
-        <v>7198721</v>
+        <v>7199019</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4721,22 +4717,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,60 +4752,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934043</v>
+        <v>128933185</v>
       </c>
       <c r="B39" t="n">
-        <v>92110</v>
+        <v>80145</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544738</v>
+        <v>544719</v>
       </c>
       <c r="R39" t="n">
-        <v>7199019</v>
+        <v>7198950</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4833,7 +4838,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,12 +4848,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,44 +4863,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933185</v>
+        <v>128933144</v>
       </c>
       <c r="B40" t="n">
-        <v>80145</v>
+        <v>80172</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544719</v>
+        <v>545205</v>
       </c>
       <c r="R40" t="n">
-        <v>7198950</v>
+        <v>7198721</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4944,22 +4944,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934059</v>
+        <v>128934018</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544753</v>
+        <v>544728</v>
       </c>
       <c r="R41" t="n">
-        <v>7199025</v>
+        <v>7198926</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,12 +5066,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5101,7 +5096,7 @@
         <v>128934063</v>
       </c>
       <c r="B42" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,10 +5205,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934018</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5221,21 +5216,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5245,13 +5240,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544728</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198926</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5280,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5290,7 +5285,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5649,7 +5649,7 @@
         <v>128934028</v>
       </c>
       <c r="B47" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R2" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
         <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>79118</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80145</v>
+        <v>91827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933927</v>
+        <v>128933206</v>
       </c>
       <c r="B7" t="n">
-        <v>79118</v>
+        <v>91556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,37 +1237,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545139</v>
+        <v>544953</v>
       </c>
       <c r="R7" t="n">
-        <v>7198701</v>
+        <v>7198881</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,27 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933206</v>
+        <v>128933927</v>
       </c>
       <c r="B8" t="n">
-        <v>91554</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,41 +1348,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544953</v>
+        <v>545139</v>
       </c>
       <c r="R8" t="n">
-        <v>7198881</v>
+        <v>7198701</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,22 +1402,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,48 +1667,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128934052</v>
+        <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>80145</v>
+        <v>92242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544774</v>
+        <v>545026</v>
       </c>
       <c r="R11" t="n">
-        <v>7199045</v>
+        <v>7198767</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,22 +1771,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934061</v>
+        <v>128934052</v>
       </c>
       <c r="B12" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,13 +1818,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544855</v>
+        <v>544774</v>
       </c>
       <c r="R12" t="n">
-        <v>7199022</v>
+        <v>7199045</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,52 +1890,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933152</v>
+        <v>128934061</v>
       </c>
       <c r="B13" t="n">
-        <v>92240</v>
+        <v>80147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545026</v>
+        <v>544855</v>
       </c>
       <c r="R13" t="n">
-        <v>7198767</v>
+        <v>7199022</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,12 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,64 +1985,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R14" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2077,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,60 +2097,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>92119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R15" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
         <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>80145</v>
+        <v>91827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R18" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B19" t="n">
-        <v>78796</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,37 +2562,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R19" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,27 +2625,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,22 +2655,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934082</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>91825</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545016</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7198794</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2733,7 +2737,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2747,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128933931</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>78798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2785,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>545235</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198698</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,22 +2839,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933148</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>128933190</v>
       </c>
       <c r="B23" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>128933194</v>
       </c>
       <c r="B24" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B27" t="n">
-        <v>91825</v>
+        <v>80147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,37 +3453,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R27" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,22 +3541,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933195</v>
+        <v>128934023</v>
       </c>
       <c r="B28" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3581,17 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544710</v>
+        <v>544764</v>
       </c>
       <c r="R28" t="n">
-        <v>7199019</v>
+        <v>7198968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>80145</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R29" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3770,7 +3770,7 @@
         <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79118</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,37 +4000,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4073,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4088,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80145</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,41 +4111,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R36" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,22 +4494,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4536,10 +4541,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,21 +4552,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4575,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R37" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4605,27 +4610,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,48 +4652,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934043</v>
+        <v>128933144</v>
       </c>
       <c r="B38" t="n">
-        <v>92117</v>
+        <v>80174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544738</v>
+        <v>545205</v>
       </c>
       <c r="R38" t="n">
-        <v>7199019</v>
+        <v>7198721</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4717,27 +4721,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,64 +4751,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933185</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>80145</v>
+        <v>92119</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544719</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198950</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4838,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4848,7 +4843,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,61 +4863,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933144</v>
+        <v>128934018</v>
       </c>
       <c r="B40" t="n">
-        <v>80172</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545205</v>
+        <v>544728</v>
       </c>
       <c r="R40" t="n">
-        <v>7198721</v>
+        <v>7198926</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4944,22 +4940,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,44 +4970,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934018</v>
+        <v>128934063</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>91953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,13 +5017,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544728</v>
+        <v>544870</v>
       </c>
       <c r="R41" t="n">
-        <v>7198926</v>
+        <v>7198981</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5056,7 +5052,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5066,7 +5062,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,48 +5094,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934063</v>
+        <v>128933185</v>
       </c>
       <c r="B42" t="n">
-        <v>91951</v>
+        <v>80147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544870</v>
+        <v>544719</v>
       </c>
       <c r="R42" t="n">
-        <v>7198981</v>
+        <v>7198950</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5163,7 +5168,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,12 +5178,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,12 +5193,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5208,7 +5208,7 @@
         <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>128933207</v>
       </c>
       <c r="B46" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>128934028</v>
       </c>
       <c r="B47" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933206</v>
+        <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>91556</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,41 +1237,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544953</v>
+        <v>545139</v>
       </c>
       <c r="R7" t="n">
-        <v>7198881</v>
+        <v>7198701</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1291,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1326,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933927</v>
+        <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>91556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,37 +1349,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545139</v>
+        <v>544953</v>
       </c>
       <c r="R8" t="n">
-        <v>7198701</v>
+        <v>7198881</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,27 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1997,48 +1997,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>92119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R14" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,64 +2101,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>92119</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R15" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934082</v>
+        <v>128934066</v>
       </c>
       <c r="B18" t="n">
-        <v>91827</v>
+        <v>80147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545016</v>
+        <v>544869</v>
       </c>
       <c r="R18" t="n">
-        <v>7198794</v>
+        <v>7198981</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933199</v>
+        <v>128934082</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,46 +2562,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544762</v>
+        <v>545016</v>
       </c>
       <c r="R19" t="n">
-        <v>7199027</v>
+        <v>7198794</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,7 +2621,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2640,7 +2631,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,22 +2646,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128933199</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,37 +2669,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>544762</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7199027</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,12 +2762,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B36" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R36" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4494,27 +4494,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4541,10 +4536,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,21 +4547,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4580,10 +4575,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R37" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4610,22 +4605,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,10 +4652,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933144</v>
+        <v>128934063</v>
       </c>
       <c r="B38" t="n">
-        <v>80174</v>
+        <v>91953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4663,41 +4663,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545205</v>
+        <v>544870</v>
       </c>
       <c r="R38" t="n">
-        <v>7198721</v>
+        <v>7198981</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4721,22 +4717,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,60 +4752,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934043</v>
+        <v>128933144</v>
       </c>
       <c r="B39" t="n">
-        <v>92119</v>
+        <v>80174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544738</v>
+        <v>545205</v>
       </c>
       <c r="R39" t="n">
-        <v>7199019</v>
+        <v>7198721</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,27 +4833,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,12 +4863,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4982,32 +4982,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934063</v>
+        <v>128934059</v>
       </c>
       <c r="B41" t="n">
-        <v>91953</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544870</v>
+        <v>544753</v>
       </c>
       <c r="R41" t="n">
-        <v>7198981</v>
+        <v>7199025</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal låga av tall</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5205,32 +5205,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934059</v>
+        <v>128934043</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>92119</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544753</v>
+        <v>544738</v>
       </c>
       <c r="R43" t="n">
-        <v>7199025</v>
+        <v>7199019</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gammla ringhack på gran</t>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -1667,52 +1667,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933152</v>
+        <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>92242</v>
+        <v>80147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545026</v>
+        <v>544774</v>
       </c>
       <c r="R11" t="n">
-        <v>7198767</v>
+        <v>7199045</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,19 +1762,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934052</v>
+        <v>128934061</v>
       </c>
       <c r="B12" t="n">
         <v>80147</v>
@@ -1818,13 +1809,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544774</v>
+        <v>544855</v>
       </c>
       <c r="R12" t="n">
-        <v>7199045</v>
+        <v>7199022</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,48 +1881,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128934061</v>
+        <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>80147</v>
+        <v>92242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544855</v>
+        <v>545026</v>
       </c>
       <c r="R13" t="n">
-        <v>7199022</v>
+        <v>7198767</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1965,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,12 +1985,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934063</v>
+        <v>128933144</v>
       </c>
       <c r="B38" t="n">
-        <v>91953</v>
+        <v>80174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4663,37 +4663,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544870</v>
+        <v>545205</v>
       </c>
       <c r="R38" t="n">
-        <v>7198981</v>
+        <v>7198721</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4717,27 +4721,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,64 +4751,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933144</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>80174</v>
+        <v>92119</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545205</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198721</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4833,22 +4828,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,44 +4863,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934018</v>
+        <v>128934063</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>91953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544728</v>
+        <v>544870</v>
       </c>
       <c r="R40" t="n">
-        <v>7198926</v>
+        <v>7198981</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,7 +4955,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4982,10 +4987,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934059</v>
+        <v>128934018</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4993,21 +4998,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5017,13 +5022,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544753</v>
+        <v>544728</v>
       </c>
       <c r="R41" t="n">
-        <v>7199025</v>
+        <v>7198926</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5052,7 +5057,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5062,12 +5067,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933185</v>
+        <v>128934059</v>
       </c>
       <c r="B42" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,41 +5105,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544719</v>
+        <v>544753</v>
       </c>
       <c r="R42" t="n">
-        <v>7198950</v>
+        <v>7199025</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5168,7 +5164,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5178,7 +5174,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,60 +5194,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934043</v>
+        <v>128933185</v>
       </c>
       <c r="B43" t="n">
-        <v>92119</v>
+        <v>80147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544738</v>
+        <v>544719</v>
       </c>
       <c r="R43" t="n">
-        <v>7199019</v>
+        <v>7198950</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5275,7 +5280,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5290,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,12 +5305,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933197</v>
+        <v>128933193</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544719</v>
+        <v>544736</v>
       </c>
       <c r="R2" t="n">
-        <v>7199038</v>
+        <v>7198995</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933193</v>
+        <v>128933210</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544736</v>
+        <v>545031</v>
       </c>
       <c r="R3" t="n">
-        <v>7198995</v>
+        <v>7198840</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>91827</v>
+        <v>80147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933203</v>
+        <v>128934048</v>
       </c>
       <c r="B9" t="n">
         <v>80147</v>
@@ -1477,24 +1477,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544919</v>
+        <v>544735</v>
       </c>
       <c r="R9" t="n">
-        <v>7198905</v>
+        <v>7199043</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,19 +1544,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934048</v>
+        <v>128933203</v>
       </c>
       <c r="B10" t="n">
         <v>80147</v>
@@ -1588,20 +1584,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544735</v>
+        <v>544919</v>
       </c>
       <c r="R10" t="n">
-        <v>7199043</v>
+        <v>7198905</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,60 +1655,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128934052</v>
+        <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>80147</v>
+        <v>92257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544774</v>
+        <v>545026</v>
       </c>
       <c r="R11" t="n">
-        <v>7199045</v>
+        <v>7198767</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,19 +1771,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934061</v>
+        <v>128934052</v>
       </c>
       <c r="B12" t="n">
         <v>80147</v>
@@ -1809,13 +1818,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544855</v>
+        <v>544774</v>
       </c>
       <c r="R12" t="n">
-        <v>7199022</v>
+        <v>7199045</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,52 +1890,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933152</v>
+        <v>128934061</v>
       </c>
       <c r="B13" t="n">
-        <v>92242</v>
+        <v>80147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545026</v>
+        <v>544855</v>
       </c>
       <c r="R13" t="n">
-        <v>7198767</v>
+        <v>7199022</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,12 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,12 +1985,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934030</v>
+        <v>128934070</v>
       </c>
       <c r="B16" t="n">
         <v>80147</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544731</v>
+        <v>544967</v>
       </c>
       <c r="R16" t="n">
-        <v>7198998</v>
+        <v>7198870</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,12 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2332,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934070</v>
+        <v>128934030</v>
       </c>
       <c r="B17" t="n">
         <v>80147</v>
@@ -2372,13 +2367,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544967</v>
+        <v>544731</v>
       </c>
       <c r="R17" t="n">
-        <v>7198870</v>
+        <v>7198998</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,7 +2402,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2412,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>80147</v>
+        <v>91837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R18" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934082</v>
+        <v>128933931</v>
       </c>
       <c r="B19" t="n">
-        <v>91827</v>
+        <v>78798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545016</v>
+        <v>545235</v>
       </c>
       <c r="R19" t="n">
-        <v>7198794</v>
+        <v>7198698</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2616,22 +2616,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,46 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2747,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,22 +2758,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,27 +2844,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3000,7 +3000,7 @@
         <v>128933190</v>
       </c>
       <c r="B23" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>128933194</v>
       </c>
       <c r="B24" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B30" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,37 +3778,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R30" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,7 +3844,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3847,7 +3854,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,28 +3863,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B31" t="n">
-        <v>91560</v>
+        <v>91554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,44 +3893,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R31" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3951,7 +3952,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3961,7 +3962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,29 +3971,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,41 +4000,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4073,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>80147</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4111,37 +4107,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4195,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4763,32 +4763,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934043</v>
+        <v>128934063</v>
       </c>
       <c r="B39" t="n">
-        <v>92119</v>
+        <v>91962</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544738</v>
+        <v>544870</v>
       </c>
       <c r="R39" t="n">
-        <v>7199019</v>
+        <v>7198981</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Högt upp gammal sälg</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4875,32 +4875,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934063</v>
+        <v>128934043</v>
       </c>
       <c r="B40" t="n">
-        <v>91953</v>
+        <v>92134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>760</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544870</v>
+        <v>544738</v>
       </c>
       <c r="R40" t="n">
-        <v>7198981</v>
+        <v>7199019</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal låga av tall</t>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934059</v>
+        <v>128933185</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,37 +5105,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544753</v>
+        <v>544719</v>
       </c>
       <c r="R42" t="n">
-        <v>7199025</v>
+        <v>7198950</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5164,7 +5168,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5174,12 +5178,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5194,22 +5193,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933185</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5217,41 +5216,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544719</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198950</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5280,7 +5275,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5290,7 +5285,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,12 +5305,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5535,52 +5535,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933207</v>
+        <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>92134</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544978</v>
+        <v>544728</v>
       </c>
       <c r="R46" t="n">
-        <v>7198868</v>
+        <v>7198999</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5609,7 +5605,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5619,7 +5615,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5634,60 +5635,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128934028</v>
+        <v>128933207</v>
       </c>
       <c r="B47" t="n">
-        <v>92119</v>
+        <v>80147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544728</v>
+        <v>544978</v>
       </c>
       <c r="R47" t="n">
-        <v>7198999</v>
+        <v>7198868</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5716,7 +5721,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5726,12 +5731,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5746,12 +5746,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933193</v>
+        <v>128933197</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736</v>
+        <v>544719</v>
       </c>
       <c r="R2" t="n">
-        <v>7198995</v>
+        <v>7199038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R3" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80147</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,52 +1008,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>80147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R5" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,60 +1103,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>80147</v>
+        <v>91963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R6" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934048</v>
+        <v>128933203</v>
       </c>
       <c r="B9" t="n">
         <v>80147</v>
@@ -1477,20 +1477,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544735</v>
+        <v>544919</v>
       </c>
       <c r="R9" t="n">
-        <v>7199043</v>
+        <v>7198905</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,19 +1548,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128933203</v>
+        <v>128934048</v>
       </c>
       <c r="B10" t="n">
         <v>80147</v>
@@ -1584,24 +1588,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544919</v>
+        <v>544735</v>
       </c>
       <c r="R10" t="n">
-        <v>7198905</v>
+        <v>7199043</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,64 +1655,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933152</v>
+        <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>92257</v>
+        <v>80147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545026</v>
+        <v>544774</v>
       </c>
       <c r="R11" t="n">
-        <v>7198767</v>
+        <v>7199045</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,60 +1762,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934052</v>
+        <v>128933152</v>
       </c>
       <c r="B12" t="n">
-        <v>80147</v>
+        <v>92258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544774</v>
+        <v>545026</v>
       </c>
       <c r="R12" t="n">
-        <v>7199045</v>
+        <v>7198767</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1858,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,12 +1878,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934070</v>
+        <v>128934030</v>
       </c>
       <c r="B16" t="n">
         <v>80147</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544967</v>
+        <v>544731</v>
       </c>
       <c r="R16" t="n">
-        <v>7198870</v>
+        <v>7198998</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934030</v>
+        <v>128934070</v>
       </c>
       <c r="B17" t="n">
         <v>80147</v>
@@ -2367,13 +2372,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544731</v>
+        <v>544967</v>
       </c>
       <c r="R17" t="n">
-        <v>7198998</v>
+        <v>7198870</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2412,12 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934082</v>
+        <v>128933199</v>
       </c>
       <c r="B18" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,37 +2455,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545016</v>
+        <v>544762</v>
       </c>
       <c r="R18" t="n">
-        <v>7198794</v>
+        <v>7199027</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2514,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,22 +2548,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933931</v>
+        <v>128934066</v>
       </c>
       <c r="B19" t="n">
-        <v>78798</v>
+        <v>80147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2571,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2595,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545235</v>
+        <v>544869</v>
       </c>
       <c r="R19" t="n">
-        <v>7198698</v>
+        <v>7198981</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2616,27 +2625,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128933931</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>78798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>545235</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7198698</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2728,22 +2732,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128934082</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2790,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>545016</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198794</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3000,7 +3000,7 @@
         <v>128933190</v>
       </c>
       <c r="B23" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>128933194</v>
       </c>
       <c r="B24" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
         <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91558</v>
+        <v>91554</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,44 +3778,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R30" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3844,7 +3837,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3854,7 +3847,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,29 +3856,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91554</v>
+        <v>91560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,37 +3885,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R31" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3952,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,13 +3966,14 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -3989,10 +3985,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,37 +3996,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80147</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,41 +4107,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4170,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4180,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,12 +4191,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4652,10 +4648,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933144</v>
+        <v>128934063</v>
       </c>
       <c r="B38" t="n">
-        <v>80174</v>
+        <v>91963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4663,41 +4659,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545205</v>
+        <v>544870</v>
       </c>
       <c r="R38" t="n">
-        <v>7198721</v>
+        <v>7198981</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4721,22 +4713,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,44 +4748,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934063</v>
+        <v>128934018</v>
       </c>
       <c r="B39" t="n">
-        <v>91962</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,13 +4795,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544870</v>
+        <v>544728</v>
       </c>
       <c r="R39" t="n">
-        <v>7198981</v>
+        <v>7198926</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4833,7 +4830,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,12 +4840,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,7 +4870,7 @@
         <v>128934043</v>
       </c>
       <c r="B40" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,45 +4979,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934018</v>
+        <v>128933144</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>80174</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544728</v>
+        <v>545205</v>
       </c>
       <c r="R41" t="n">
-        <v>7198926</v>
+        <v>7198721</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5052,22 +5048,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5082,22 +5078,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933185</v>
+        <v>128934059</v>
       </c>
       <c r="B42" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,41 +5101,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544719</v>
+        <v>544753</v>
       </c>
       <c r="R42" t="n">
-        <v>7198950</v>
+        <v>7199025</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5168,7 +5160,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5178,7 +5170,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,22 +5190,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934059</v>
+        <v>128933185</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5216,37 +5213,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544753</v>
+        <v>544719</v>
       </c>
       <c r="R43" t="n">
-        <v>7199025</v>
+        <v>7198950</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5275,7 +5276,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5285,12 +5286,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,12 +5301,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5535,48 +5531,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128934028</v>
+        <v>128933207</v>
       </c>
       <c r="B46" t="n">
-        <v>92134</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544728</v>
+        <v>544978</v>
       </c>
       <c r="R46" t="n">
-        <v>7198999</v>
+        <v>7198868</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5615,12 +5615,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5635,64 +5630,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933207</v>
+        <v>128934028</v>
       </c>
       <c r="B47" t="n">
-        <v>80147</v>
+        <v>92135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544978</v>
+        <v>544728</v>
       </c>
       <c r="R47" t="n">
-        <v>7198868</v>
+        <v>7198999</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5721,7 +5712,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5731,7 +5722,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5746,12 +5742,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R2" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933193</v>
+        <v>128933197</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>80147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544736</v>
+        <v>544719</v>
       </c>
       <c r="R3" t="n">
-        <v>7198995</v>
+        <v>7199038</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1667,48 +1667,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128934052</v>
+        <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>80147</v>
+        <v>92258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544774</v>
+        <v>545026</v>
       </c>
       <c r="R11" t="n">
-        <v>7199045</v>
+        <v>7198767</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,64 +1771,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933152</v>
+        <v>128934052</v>
       </c>
       <c r="B12" t="n">
-        <v>92258</v>
+        <v>80147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545026</v>
+        <v>544774</v>
       </c>
       <c r="R12" t="n">
-        <v>7198767</v>
+        <v>7199045</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1848,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,12 +1878,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1997,52 +1997,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B14" t="n">
-        <v>92135</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R14" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2077,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,60 +2097,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>92135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R15" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933199</v>
+        <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,46 +2455,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544762</v>
+        <v>545016</v>
       </c>
       <c r="R18" t="n">
-        <v>7199027</v>
+        <v>7198794</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2523,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,12 +2539,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2667,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,37 +2669,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R20" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,27 +2732,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,22 +2762,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934082</v>
+        <v>128933931</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>78798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2814,10 +2809,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545016</v>
+        <v>545235</v>
       </c>
       <c r="R21" t="n">
-        <v>7198794</v>
+        <v>7198698</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2844,22 +2839,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933195</v>
+        <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>80147</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,41 +3453,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544710</v>
+        <v>545027</v>
       </c>
       <c r="R27" t="n">
-        <v>7199019</v>
+        <v>7198834</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3516,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,19 +3537,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934023</v>
+        <v>128933195</v>
       </c>
       <c r="B28" t="n">
         <v>80147</v>
@@ -3581,17 +3577,21 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544764</v>
+        <v>544710</v>
       </c>
       <c r="R28" t="n">
-        <v>7198968</v>
+        <v>7199019</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934080</v>
+        <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>80147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545027</v>
+        <v>544764</v>
       </c>
       <c r="R29" t="n">
-        <v>7198834</v>
+        <v>7198968</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4648,48 +4648,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934063</v>
+        <v>128933185</v>
       </c>
       <c r="B38" t="n">
-        <v>91963</v>
+        <v>80147</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544870</v>
+        <v>544719</v>
       </c>
       <c r="R38" t="n">
-        <v>7198981</v>
+        <v>7198950</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4718,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4728,12 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4748,57 +4747,61 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934018</v>
+        <v>128933144</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>80174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544728</v>
+        <v>545205</v>
       </c>
       <c r="R39" t="n">
-        <v>7198926</v>
+        <v>7198721</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4825,22 +4828,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4855,44 +4858,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934043</v>
+        <v>128934018</v>
       </c>
       <c r="B40" t="n">
-        <v>92135</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4902,13 +4905,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544738</v>
+        <v>544728</v>
       </c>
       <c r="R40" t="n">
-        <v>7199019</v>
+        <v>7198926</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4937,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,12 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4979,52 +4977,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933144</v>
+        <v>128934043</v>
       </c>
       <c r="B41" t="n">
-        <v>80174</v>
+        <v>92135</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>760</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545205</v>
+        <v>544738</v>
       </c>
       <c r="R41" t="n">
-        <v>7198721</v>
+        <v>7199019</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5048,22 +5042,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5078,12 +5077,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5202,52 +5201,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933185</v>
+        <v>128934063</v>
       </c>
       <c r="B43" t="n">
-        <v>80147</v>
+        <v>91963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544719</v>
+        <v>544870</v>
       </c>
       <c r="R43" t="n">
-        <v>7198950</v>
+        <v>7198981</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5276,7 +5271,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5286,7 +5281,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,12 +5301,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>79122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R2" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B3" t="n">
-        <v>80147</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R3" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933193</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544736</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198995</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,48 +1008,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>80147</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R5" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,64 +1107,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R6" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
         <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,52 +1667,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933152</v>
+        <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>92258</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545026</v>
+        <v>544774</v>
       </c>
       <c r="R11" t="n">
-        <v>7198767</v>
+        <v>7199045</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,22 +1762,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934052</v>
+        <v>128934061</v>
       </c>
       <c r="B12" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,13 +1809,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544774</v>
+        <v>544855</v>
       </c>
       <c r="R12" t="n">
-        <v>7199045</v>
+        <v>7199022</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,48 +1881,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128934061</v>
+        <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>80147</v>
+        <v>92261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544855</v>
+        <v>545026</v>
       </c>
       <c r="R13" t="n">
-        <v>7199022</v>
+        <v>7198767</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1965,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,60 +1985,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933935</v>
+        <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>92138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545232</v>
+        <v>544732</v>
       </c>
       <c r="R14" t="n">
-        <v>7198595</v>
+        <v>7199023</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tall!</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,64 +2101,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933198</v>
+        <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>92135</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544732</v>
+        <v>545232</v>
       </c>
       <c r="R15" t="n">
-        <v>7199023</v>
+        <v>7198595</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
         <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934082</v>
+        <v>128933931</v>
       </c>
       <c r="B18" t="n">
-        <v>91838</v>
+        <v>78800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545016</v>
+        <v>545235</v>
       </c>
       <c r="R18" t="n">
-        <v>7198794</v>
+        <v>7198698</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2509,22 +2509,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B19" t="n">
-        <v>80147</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2567,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R19" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2621,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2631,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,46 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2747,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,22 +2758,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933931</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545235</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198698</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,27 +2844,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933148</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>128933190</v>
       </c>
       <c r="B23" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>128933194</v>
       </c>
       <c r="B24" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>128933195</v>
       </c>
       <c r="B28" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>79122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,41 +3996,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4055,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4065,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4080,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,37 +4103,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,12 +4191,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4206,7 +4206,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R36" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4490,22 +4490,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4532,10 +4537,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,21 +4548,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4571,10 +4576,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R37" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4601,27 +4606,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,52 +4648,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933185</v>
+        <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>80147</v>
+        <v>92138</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544719</v>
+        <v>544738</v>
       </c>
       <c r="R38" t="n">
-        <v>7198950</v>
+        <v>7199019</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4718,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4728,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4747,22 +4748,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933144</v>
+        <v>128934063</v>
       </c>
       <c r="B39" t="n">
-        <v>80174</v>
+        <v>91966</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,41 +4771,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545205</v>
+        <v>544870</v>
       </c>
       <c r="R39" t="n">
-        <v>7198721</v>
+        <v>7198981</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,22 +4825,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,12 +4860,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4873,7 +4875,7 @@
         <v>128934018</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,32 +4979,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934043</v>
+        <v>128934059</v>
       </c>
       <c r="B41" t="n">
-        <v>92135</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5014,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544738</v>
+        <v>544753</v>
       </c>
       <c r="R41" t="n">
-        <v>7199019</v>
+        <v>7199025</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5047,7 +5049,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,12 +5059,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Högt upp gammal sälg</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5089,10 +5091,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934059</v>
+        <v>128933185</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,37 +5102,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544753</v>
+        <v>544719</v>
       </c>
       <c r="R42" t="n">
-        <v>7199025</v>
+        <v>7198950</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5159,7 +5165,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5169,12 +5175,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5189,22 +5190,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934063</v>
+        <v>128933144</v>
       </c>
       <c r="B43" t="n">
-        <v>91963</v>
+        <v>80176</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5212,37 +5213,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4217</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544870</v>
+        <v>545205</v>
       </c>
       <c r="R43" t="n">
-        <v>7198981</v>
+        <v>7198721</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5266,27 +5271,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,12 +5301,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5531,52 +5531,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933207</v>
+        <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>92138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544978</v>
+        <v>544728</v>
       </c>
       <c r="R46" t="n">
-        <v>7198868</v>
+        <v>7198999</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5605,7 +5601,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5615,7 +5611,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5630,60 +5631,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128934028</v>
+        <v>128933207</v>
       </c>
       <c r="B47" t="n">
-        <v>92135</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544728</v>
+        <v>544978</v>
       </c>
       <c r="R47" t="n">
-        <v>7198999</v>
+        <v>7198868</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5712,7 +5717,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5722,12 +5727,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5742,12 +5742,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933927</v>
+        <v>128933206</v>
       </c>
       <c r="B7" t="n">
-        <v>79122</v>
+        <v>91557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,37 +1237,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545139</v>
+        <v>544953</v>
       </c>
       <c r="R7" t="n">
-        <v>7198701</v>
+        <v>7198881</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,27 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933206</v>
+        <v>128933927</v>
       </c>
       <c r="B8" t="n">
-        <v>91557</v>
+        <v>79122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,41 +1348,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544953</v>
+        <v>545139</v>
       </c>
       <c r="R8" t="n">
-        <v>7198881</v>
+        <v>7198701</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,22 +1402,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933193</v>
+        <v>128933197</v>
       </c>
       <c r="B2" t="n">
-        <v>79122</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736</v>
+        <v>544719</v>
       </c>
       <c r="R2" t="n">
-        <v>7198995</v>
+        <v>7199038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933210</v>
+        <v>128933193</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>79123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545031</v>
+        <v>544736</v>
       </c>
       <c r="R3" t="n">
-        <v>7198840</v>
+        <v>7198995</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>91843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>91966</v>
+        <v>91968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933206</v>
+        <v>128933927</v>
       </c>
       <c r="B7" t="n">
-        <v>91557</v>
+        <v>79123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,41 +1237,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544953</v>
+        <v>545139</v>
       </c>
       <c r="R7" t="n">
-        <v>7198881</v>
+        <v>7198701</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1291,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1326,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933927</v>
+        <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>79122</v>
+        <v>91559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,37 +1349,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545139</v>
+        <v>544953</v>
       </c>
       <c r="R8" t="n">
-        <v>7198701</v>
+        <v>7198881</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,27 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         <v>128933203</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128934048</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>128934052</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>128934061</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>128933152</v>
       </c>
       <c r="B13" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128933935</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128934030</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128934070</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933931</v>
+        <v>128934066</v>
       </c>
       <c r="B18" t="n">
-        <v>78800</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545235</v>
+        <v>544869</v>
       </c>
       <c r="R18" t="n">
-        <v>7198698</v>
+        <v>7198981</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2509,27 +2509,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934082</v>
+        <v>128933931</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2591,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545016</v>
+        <v>545235</v>
       </c>
       <c r="R19" t="n">
-        <v>7198794</v>
+        <v>7198698</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2621,22 +2616,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128933199</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>544762</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7199027</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2742,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2752,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,22 +2767,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128934082</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2790,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>545016</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198794</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,49 +2874,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933148</v>
+        <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>92140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545231</v>
+        <v>544731</v>
       </c>
       <c r="R22" t="n">
-        <v>7198599</v>
+        <v>7198999</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933190</v>
+        <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,19 +3032,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544731</v>
+        <v>544710</v>
       </c>
       <c r="R23" t="n">
-        <v>7198999</v>
+        <v>7199001</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3081,12 +3089,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3095,6 +3098,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3106,39 +3110,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933194</v>
+        <v>128933148</v>
       </c>
       <c r="B24" t="n">
-        <v>92138</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3146,19 +3150,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544710</v>
+        <v>545231</v>
       </c>
       <c r="R24" t="n">
-        <v>7199001</v>
+        <v>7198599</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3201,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,7 +3210,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>128934045</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128934050</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128934080</v>
       </c>
       <c r="B27" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>128933195</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B32" t="n">
-        <v>79122</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,37 +3996,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4065,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>79123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4103,41 +4107,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,12 +4191,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4206,7 +4206,7 @@
         <v>128934040</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128933205</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B36" t="n">
-        <v>78800</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R36" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4490,27 +4490,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4537,10 +4532,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4548,21 +4543,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R37" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4606,22 +4601,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,32 +4648,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934043</v>
+        <v>128934018</v>
       </c>
       <c r="B38" t="n">
-        <v>92138</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544738</v>
+        <v>544728</v>
       </c>
       <c r="R38" t="n">
-        <v>7199019</v>
+        <v>7198926</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4728,12 +4728,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Högt upp gammal sälg</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,48 +4755,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934063</v>
+        <v>128933185</v>
       </c>
       <c r="B39" t="n">
-        <v>91966</v>
+        <v>80150</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544870</v>
+        <v>544719</v>
       </c>
       <c r="R39" t="n">
-        <v>7198981</v>
+        <v>7198950</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4830,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,12 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4860,44 +4854,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934018</v>
+        <v>128934043</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>92140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4907,13 +4901,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544728</v>
+        <v>544738</v>
       </c>
       <c r="R40" t="n">
-        <v>7198926</v>
+        <v>7199019</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4942,7 +4936,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4952,7 +4946,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4979,32 +4978,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934059</v>
+        <v>128934063</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5014,10 +5013,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544753</v>
+        <v>544870</v>
       </c>
       <c r="R41" t="n">
-        <v>7199025</v>
+        <v>7198981</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5049,7 +5048,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5059,12 +5058,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gammla ringhack på gran</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5091,32 +5090,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933185</v>
+        <v>128933144</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80177</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5130,10 +5129,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544719</v>
+        <v>545205</v>
       </c>
       <c r="R42" t="n">
-        <v>7198950</v>
+        <v>7198721</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5160,22 +5159,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5202,52 +5201,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933144</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>80176</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545205</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198721</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5271,22 +5266,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,12 +5301,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
         <v>128933186</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>128934076</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>128933207</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933197</v>
+        <v>128933193</v>
       </c>
       <c r="B2" t="n">
-        <v>80150</v>
+        <v>79123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544719</v>
+        <v>544736</v>
       </c>
       <c r="R2" t="n">
-        <v>7199038</v>
+        <v>7198995</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933193</v>
+        <v>128933210</v>
       </c>
       <c r="B3" t="n">
-        <v>79123</v>
+        <v>91847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544736</v>
+        <v>545031</v>
       </c>
       <c r="R3" t="n">
-        <v>7198995</v>
+        <v>7198840</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B4" t="n">
-        <v>91843</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,52 +1008,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B5" t="n">
-        <v>91968</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R5" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,60 +1103,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>91972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R6" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1667,48 +1667,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128934052</v>
+        <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>80150</v>
+        <v>92267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544774</v>
+        <v>545026</v>
       </c>
       <c r="R11" t="n">
-        <v>7199045</v>
+        <v>7198767</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,19 +1771,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934061</v>
+        <v>128934052</v>
       </c>
       <c r="B12" t="n">
         <v>80150</v>
@@ -1809,13 +1818,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544855</v>
+        <v>544774</v>
       </c>
       <c r="R12" t="n">
-        <v>7199022</v>
+        <v>7199045</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,52 +1890,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933152</v>
+        <v>128934061</v>
       </c>
       <c r="B13" t="n">
-        <v>92263</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545026</v>
+        <v>544855</v>
       </c>
       <c r="R13" t="n">
-        <v>7198767</v>
+        <v>7199022</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,12 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nyligen fallen gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,12 +1985,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>91847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R18" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,46 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R20" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2742,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2752,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,22 +2758,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934082</v>
+        <v>128933199</v>
       </c>
       <c r="B21" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,37 +2781,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545016</v>
+        <v>544762</v>
       </c>
       <c r="R21" t="n">
-        <v>7198794</v>
+        <v>7199027</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128934080</v>
+        <v>128933195</v>
       </c>
       <c r="B27" t="n">
-        <v>91843</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,37 +3453,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545027</v>
+        <v>544710</v>
       </c>
       <c r="R27" t="n">
-        <v>7198834</v>
+        <v>7199019</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,19 +3541,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933195</v>
+        <v>128934023</v>
       </c>
       <c r="B28" t="n">
         <v>80150</v>
@@ -3577,21 +3581,17 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544710</v>
+        <v>544764</v>
       </c>
       <c r="R28" t="n">
-        <v>7199019</v>
+        <v>7198968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3648,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>91847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R29" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3770,7 +3770,7 @@
         <v>128934068</v>
       </c>
       <c r="B30" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>128933150</v>
       </c>
       <c r="B31" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933196</v>
+        <v>128934035</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79123</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,41 +3996,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544719</v>
+        <v>544725</v>
       </c>
       <c r="R32" t="n">
-        <v>7198986</v>
+        <v>7198996</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4059,7 +4055,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4065,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,22 +4080,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128934035</v>
+        <v>128933196</v>
       </c>
       <c r="B33" t="n">
-        <v>79123</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,37 +4103,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544725</v>
+        <v>544719</v>
       </c>
       <c r="R33" t="n">
-        <v>7198996</v>
+        <v>7198986</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,12 +4191,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4648,32 +4648,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934018</v>
+        <v>128934043</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>92144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544728</v>
+        <v>544738</v>
       </c>
       <c r="R38" t="n">
-        <v>7198926</v>
+        <v>7199019</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4728,7 +4728,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4755,32 +4760,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933185</v>
+        <v>128933144</v>
       </c>
       <c r="B39" t="n">
-        <v>80150</v>
+        <v>80177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4794,10 +4799,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544719</v>
+        <v>545205</v>
       </c>
       <c r="R39" t="n">
-        <v>7198950</v>
+        <v>7198721</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4824,22 +4829,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4866,32 +4871,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934043</v>
+        <v>128934059</v>
       </c>
       <c r="B40" t="n">
-        <v>92140</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4901,10 +4906,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544738</v>
+        <v>544753</v>
       </c>
       <c r="R40" t="n">
-        <v>7199019</v>
+        <v>7199025</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4936,7 +4941,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4946,12 +4951,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Högt upp gammal sälg</t>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,48 +4983,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128934063</v>
+        <v>128933185</v>
       </c>
       <c r="B41" t="n">
-        <v>91968</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544870</v>
+        <v>544719</v>
       </c>
       <c r="R41" t="n">
-        <v>7198981</v>
+        <v>7198950</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5048,7 +5057,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5058,12 +5067,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5078,22 +5082,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933144</v>
+        <v>128934063</v>
       </c>
       <c r="B42" t="n">
-        <v>80177</v>
+        <v>91972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,41 +5105,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545205</v>
+        <v>544870</v>
       </c>
       <c r="R42" t="n">
-        <v>7198721</v>
+        <v>7198981</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5159,22 +5159,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5189,22 +5194,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934059</v>
+        <v>128934018</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5212,21 +5217,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5236,13 +5241,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544753</v>
+        <v>544728</v>
       </c>
       <c r="R43" t="n">
-        <v>7199025</v>
+        <v>7198926</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5271,7 +5276,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5281,12 +5286,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5534,7 +5534,7 @@
         <v>128934028</v>
       </c>
       <c r="B46" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933210</v>
+        <v>128933197</v>
       </c>
       <c r="B3" t="n">
-        <v>91847</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545031</v>
+        <v>544719</v>
       </c>
       <c r="R3" t="n">
-        <v>7198840</v>
+        <v>7199038</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933197</v>
+        <v>128933210</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544719</v>
+        <v>545031</v>
       </c>
       <c r="R4" t="n">
-        <v>7199038</v>
+        <v>7198840</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,48 +1008,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934057</v>
+        <v>128933201</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>91973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544740</v>
+        <v>544868</v>
       </c>
       <c r="R5" t="n">
-        <v>7198998</v>
+        <v>7198977</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,64 +1107,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933201</v>
+        <v>128934057</v>
       </c>
       <c r="B6" t="n">
-        <v>91972</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544868</v>
+        <v>544740</v>
       </c>
       <c r="R6" t="n">
-        <v>7198977</v>
+        <v>7198998</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
         <v>128933206</v>
       </c>
       <c r="B8" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         <v>128933152</v>
       </c>
       <c r="B11" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>128933198</v>
       </c>
       <c r="B14" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934082</v>
+        <v>128933199</v>
       </c>
       <c r="B18" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,37 +2455,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545016</v>
+        <v>544762</v>
       </c>
       <c r="R18" t="n">
-        <v>7198794</v>
+        <v>7199027</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2514,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,12 +2548,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2663,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934066</v>
+        <v>128934082</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544869</v>
+        <v>545016</v>
       </c>
       <c r="R20" t="n">
-        <v>7198981</v>
+        <v>7198794</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2733,7 +2742,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2752,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,17 +2772,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933199</v>
+        <v>128934066</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,46 +2790,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544762</v>
+        <v>544869</v>
       </c>
       <c r="R21" t="n">
-        <v>7199027</v>
+        <v>7198981</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,12 +2874,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
         <v>128933190</v>
       </c>
       <c r="B22" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>128933194</v>
       </c>
       <c r="B23" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934023</v>
+        <v>128934080</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>91848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544764</v>
+        <v>545027</v>
       </c>
       <c r="R28" t="n">
-        <v>7198968</v>
+        <v>7198834</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934080</v>
+        <v>128934023</v>
       </c>
       <c r="B29" t="n">
-        <v>91847</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545027</v>
+        <v>544764</v>
       </c>
       <c r="R29" t="n">
-        <v>7198834</v>
+        <v>7198968</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,17 +3760,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128934068</v>
+        <v>128933150</v>
       </c>
       <c r="B30" t="n">
-        <v>91563</v>
+        <v>91570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,37 +3778,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544950</v>
+        <v>545026</v>
       </c>
       <c r="R30" t="n">
-        <v>7198872</v>
+        <v>7198734</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3847,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,13 +3859,14 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -3874,10 +3878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933150</v>
+        <v>128934068</v>
       </c>
       <c r="B31" t="n">
-        <v>91569</v>
+        <v>91564</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,40 +3889,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545026</v>
+        <v>544950</v>
       </c>
       <c r="R31" t="n">
-        <v>7198734</v>
+        <v>7198872</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3947,7 +3948,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3958,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3966,19 +3967,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933200</v>
+        <v>128933146</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544848</v>
+        <v>545239</v>
       </c>
       <c r="R36" t="n">
-        <v>7199018</v>
+        <v>7198695</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4490,22 +4490,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4532,10 +4537,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933146</v>
+        <v>128933200</v>
       </c>
       <c r="B37" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,21 +4548,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4571,10 +4576,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545239</v>
+        <v>544848</v>
       </c>
       <c r="R37" t="n">
-        <v>7198695</v>
+        <v>7199018</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4601,27 +4606,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,32 +4648,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934043</v>
+        <v>128934063</v>
       </c>
       <c r="B38" t="n">
-        <v>92144</v>
+        <v>91973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544738</v>
+        <v>544870</v>
       </c>
       <c r="R38" t="n">
-        <v>7199019</v>
+        <v>7198981</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Högt upp gammal sälg</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4753,59 +4753,55 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933144</v>
+        <v>128934043</v>
       </c>
       <c r="B39" t="n">
-        <v>80177</v>
+        <v>92145</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545205</v>
+        <v>544738</v>
       </c>
       <c r="R39" t="n">
-        <v>7198721</v>
+        <v>7199019</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,22 +4825,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4859,22 +4860,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934059</v>
+        <v>128933185</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4882,37 +4883,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544753</v>
+        <v>544719</v>
       </c>
       <c r="R40" t="n">
-        <v>7199025</v>
+        <v>7198950</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4941,7 +4946,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4951,12 +4956,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4971,44 +4971,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933185</v>
+        <v>128933144</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544719</v>
+        <v>545205</v>
       </c>
       <c r="R41" t="n">
-        <v>7198950</v>
+        <v>7198721</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5052,22 +5052,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5094,32 +5094,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934063</v>
+        <v>128934018</v>
       </c>
       <c r="B42" t="n">
-        <v>91972</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5129,13 +5129,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544870</v>
+        <v>544728</v>
       </c>
       <c r="R42" t="n">
-        <v>7198981</v>
+        <v>7198926</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5174,12 +5174,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5199,17 +5194,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934018</v>
+        <v>128934059</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5217,21 +5212,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5241,13 +5236,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544728</v>
+        <v>544753</v>
       </c>
       <c r="R43" t="n">
-        <v>7198926</v>
+        <v>7199025</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5276,7 +5271,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5286,7 +5281,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5524,55 +5524,59 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128934028</v>
+        <v>128933207</v>
       </c>
       <c r="B46" t="n">
-        <v>92144</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544728</v>
+        <v>544978</v>
       </c>
       <c r="R46" t="n">
-        <v>7198999</v>
+        <v>7198868</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5601,7 +5605,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5611,12 +5615,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5631,64 +5630,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933207</v>
+        <v>128934028</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>92145</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544978</v>
+        <v>544728</v>
       </c>
       <c r="R47" t="n">
-        <v>7198868</v>
+        <v>7198999</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5717,7 +5712,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5727,7 +5722,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5742,12 +5742,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 19506-2025 artfynd.xlsx
+++ b/artfynd/A 19506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933193</v>
+        <v>128933210</v>
       </c>
       <c r="B2" t="n">
-        <v>79123</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736</v>
+        <v>545031</v>
       </c>
       <c r="R2" t="n">
-        <v>7198995</v>
+        <v>7198840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933197</v>
+        <v>128934080</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,41 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544719</v>
+        <v>545027</v>
       </c>
       <c r="R3" t="n">
-        <v>7199038</v>
+        <v>7198834</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933210</v>
+        <v>128934082</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,24 +921,20 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545031</v>
+        <v>545016</v>
       </c>
       <c r="R4" t="n">
-        <v>7198840</v>
+        <v>7198794</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,49 +988,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933201</v>
+        <v>128933190</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544868</v>
+        <v>544731</v>
       </c>
       <c r="R5" t="n">
-        <v>7198977</v>
+        <v>7198999</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1084,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar, 2 i gott skick.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,48 +1116,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934057</v>
+        <v>128933194</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544740</v>
+        <v>544710</v>
       </c>
       <c r="R6" t="n">
-        <v>7198998</v>
+        <v>7199001</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,66 +1212,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933927</v>
+        <v>128933198</v>
       </c>
       <c r="B7" t="n">
-        <v>79123</v>
+        <v>92509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545139</v>
+        <v>544732</v>
       </c>
       <c r="R7" t="n">
-        <v>7198701</v>
+        <v>7199023</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,27 +1300,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>5m upp i luften. Bekräftad med doft.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,64 +1335,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933206</v>
+        <v>128934028</v>
       </c>
       <c r="B8" t="n">
-        <v>91564</v>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544953</v>
+        <v>544728</v>
       </c>
       <c r="R8" t="n">
-        <v>7198881</v>
+        <v>7198999</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>5st fruktkroppar på gammal sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,64 +1447,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933203</v>
+        <v>128934043</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>92509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544919</v>
+        <v>544738</v>
       </c>
       <c r="R9" t="n">
-        <v>7198905</v>
+        <v>7199019</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1539,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Högt upp gammal sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934048</v>
+        <v>128933193</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,37 +1582,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544735</v>
+        <v>544736</v>
       </c>
       <c r="R10" t="n">
-        <v>7199043</v>
+        <v>7198995</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,64 +1670,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933152</v>
+        <v>128933927</v>
       </c>
       <c r="B11" t="n">
-        <v>92268</v>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545026</v>
+        <v>545139</v>
       </c>
       <c r="R11" t="n">
-        <v>7198767</v>
+        <v>7198701</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,27 +1747,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nyligen fallen gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,22 +1782,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934052</v>
+        <v>128934035</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1818,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544774</v>
+        <v>544725</v>
       </c>
       <c r="R12" t="n">
-        <v>7199045</v>
+        <v>7198996</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,17 +1894,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128934061</v>
+        <v>128933154</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,37 +1912,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544855</v>
+        <v>544968</v>
       </c>
       <c r="R13" t="n">
-        <v>7199022</v>
+        <v>7198730</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1985,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,64 +2005,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933198</v>
+        <v>128934084</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544732</v>
+        <v>544966</v>
       </c>
       <c r="R14" t="n">
-        <v>7199023</v>
+        <v>7198729</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2081,12 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>5m upp i luften. Bekräftad med doft.</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,60 +2112,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933935</v>
+        <v>128933206</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545232</v>
+        <v>544953</v>
       </c>
       <c r="R15" t="n">
-        <v>7198595</v>
+        <v>7198881</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2193,12 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tall!</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,44 +2223,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128934030</v>
+        <v>128934068</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544731</v>
+        <v>544950</v>
       </c>
       <c r="R16" t="n">
-        <v>7198998</v>
+        <v>7198872</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2295,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,12 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,17 +2335,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128934070</v>
+        <v>128933185</v>
       </c>
       <c r="B17" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,20 +2370,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544967</v>
+        <v>544719</v>
       </c>
       <c r="R17" t="n">
-        <v>7198870</v>
+        <v>7198950</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,7 +2416,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2426,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,22 +2441,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933199</v>
+        <v>128933186</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2464,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2477,21 +2486,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544762</v>
+        <v>544721</v>
       </c>
       <c r="R18" t="n">
-        <v>7199027</v>
+        <v>7198962</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933931</v>
+        <v>128933195</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,37 +2575,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545235</v>
+        <v>544710</v>
       </c>
       <c r="R19" t="n">
-        <v>7198698</v>
+        <v>7199019</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,27 +2633,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På död stående kelo</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,22 +2663,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934082</v>
+        <v>128933196</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2683,37 +2686,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545016</v>
+        <v>544719</v>
       </c>
       <c r="R20" t="n">
-        <v>7198794</v>
+        <v>7198986</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2742,7 +2749,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2752,7 +2759,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,22 +2774,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934066</v>
+        <v>128933197</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,20 +2814,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544869</v>
+        <v>544719</v>
       </c>
       <c r="R21" t="n">
-        <v>7198981</v>
+        <v>7199038</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2870,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,49 +2885,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933190</v>
+        <v>128933203</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2925,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544731</v>
+        <v>544919</v>
       </c>
       <c r="R22" t="n">
-        <v>7198999</v>
+        <v>7198905</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,12 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar, 2 i gott skick.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,32 +3008,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933194</v>
+        <v>128933205</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3035,19 +3041,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544710</v>
+        <v>544955</v>
       </c>
       <c r="R23" t="n">
-        <v>7199001</v>
+        <v>7198870</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3079,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,7 +3101,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3110,17 +3112,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933148</v>
+        <v>128933207</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3156,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545231</v>
+        <v>544978</v>
       </c>
       <c r="R24" t="n">
-        <v>7198599</v>
+        <v>7198868</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3191,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3201,7 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128934045</v>
+        <v>128934023</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,13 +3265,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544734</v>
+        <v>544764</v>
       </c>
       <c r="R25" t="n">
-        <v>7199042</v>
+        <v>7198968</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3300,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3310,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,17 +3330,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128934050</v>
+        <v>128934030</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3370,13 +3372,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544761</v>
+        <v>544731</v>
       </c>
       <c r="R26" t="n">
-        <v>7199063</v>
+        <v>7198998</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3407,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3417,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,17 +3442,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933195</v>
+        <v>128934040</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,24 +3477,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544710</v>
+        <v>544733</v>
       </c>
       <c r="R27" t="n">
         <v>7199019</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3516,7 +3519,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3529,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,22 +3544,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128934080</v>
+        <v>128934045</v>
       </c>
       <c r="B28" t="n">
-        <v>91848</v>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,21 +3567,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3588,13 +3591,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545027</v>
+        <v>544734</v>
       </c>
       <c r="R28" t="n">
-        <v>7198834</v>
+        <v>7199042</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,7 +3626,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3633,7 +3636,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3653,17 +3656,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128934023</v>
+        <v>128934048</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3695,13 +3698,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544764</v>
+        <v>544735</v>
       </c>
       <c r="R29" t="n">
-        <v>7198968</v>
+        <v>7199043</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3740,7 +3743,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,17 +3763,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933150</v>
+        <v>128934050</v>
       </c>
       <c r="B30" t="n">
-        <v>91570</v>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,40 +3781,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545026</v>
+        <v>544761</v>
       </c>
       <c r="R30" t="n">
-        <v>7198734</v>
+        <v>7199063</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3859,14 +3859,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -3878,10 +3877,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128934068</v>
+        <v>128934052</v>
       </c>
       <c r="B31" t="n">
-        <v>91564</v>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3889,21 +3888,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3913,13 +3912,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544950</v>
+        <v>544774</v>
       </c>
       <c r="R31" t="n">
-        <v>7198872</v>
+        <v>7199045</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3958,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3978,17 +3977,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128934035</v>
+        <v>128934057</v>
       </c>
       <c r="B32" t="n">
-        <v>79123</v>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,21 +3995,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4020,13 +4019,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544725</v>
+        <v>544740</v>
       </c>
       <c r="R32" t="n">
-        <v>7198996</v>
+        <v>7198998</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4055,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4065,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4085,17 +4084,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933196</v>
+        <v>128934061</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4120,24 +4119,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544719</v>
+        <v>544855</v>
       </c>
       <c r="R33" t="n">
-        <v>7198986</v>
+        <v>7199022</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4166,7 +4161,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4171,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,22 +4186,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128934040</v>
+        <v>128934066</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,10 +4233,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544733</v>
+        <v>544869</v>
       </c>
       <c r="R34" t="n">
-        <v>7199019</v>
+        <v>7198981</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4273,7 +4268,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4283,7 +4278,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,17 +4298,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933205</v>
+        <v>128934070</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4338,24 +4333,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544955</v>
+        <v>544967</v>
       </c>
       <c r="R35" t="n">
         <v>7198870</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4384,7 +4375,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4394,7 +4385,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,22 +4400,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933146</v>
+        <v>128934076</v>
       </c>
       <c r="B36" t="n">
-        <v>78801</v>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,41 +4423,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545239</v>
+        <v>544977</v>
       </c>
       <c r="R36" t="n">
-        <v>7198695</v>
+        <v>7198853</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4490,27 +4477,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stående brandstubbe</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,44 +4507,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933200</v>
+        <v>128933152</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>92632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4576,10 +4558,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544848</v>
+        <v>545026</v>
       </c>
       <c r="R37" t="n">
-        <v>7199018</v>
+        <v>7198767</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4611,7 +4593,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4621,7 +4603,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Nyligen fallen gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,10 +4635,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934063</v>
+        <v>128933201</v>
       </c>
       <c r="B38" t="n">
-        <v>91973</v>
+        <v>92333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4676,20 +4663,24 @@
           <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544870</v>
+        <v>544868</v>
       </c>
       <c r="R38" t="n">
-        <v>7198981</v>
+        <v>7198977</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4718,7 +4709,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4728,12 +4719,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal låga av tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4748,44 +4734,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934043</v>
+        <v>128934063</v>
       </c>
       <c r="B39" t="n">
-        <v>92145</v>
+        <v>92333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4795,10 +4781,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544738</v>
+        <v>544870</v>
       </c>
       <c r="R39" t="n">
-        <v>7199019</v>
+        <v>7198981</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4830,7 +4816,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4840,12 +4826,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Högt upp gammal sälg</t>
+          <t>På gammal låga av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4865,59 +4851,55 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933185</v>
+        <v>128933947</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544719</v>
+        <v>544971</v>
       </c>
       <c r="R40" t="n">
-        <v>7198950</v>
+        <v>7198722</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4946,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4956,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4971,44 +4953,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933144</v>
+        <v>128933148</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5022,10 +5004,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545205</v>
+        <v>545231</v>
       </c>
       <c r="R41" t="n">
-        <v>7198721</v>
+        <v>7198599</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5052,22 +5034,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5094,14 +5076,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128934018</v>
+        <v>128933182</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5122,17 +5104,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544728</v>
+        <v>544696</v>
       </c>
       <c r="R42" t="n">
-        <v>7198926</v>
+        <v>7198934</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5164,7 +5150,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5174,7 +5160,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5189,60 +5175,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128934059</v>
+        <v>128933200</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544753</v>
+        <v>544848</v>
       </c>
       <c r="R43" t="n">
-        <v>7199025</v>
+        <v>7199018</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5271,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5281,12 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gammla ringhack på gran</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,64 +5286,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933186</v>
+        <v>128933935</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544721</v>
+        <v>545232</v>
       </c>
       <c r="R44" t="n">
-        <v>7198962</v>
+        <v>7198595</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5387,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5397,7 +5378,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,44 +5398,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128934076</v>
+        <v>128934018</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5459,13 +5445,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544977</v>
+        <v>544728</v>
       </c>
       <c r="R45" t="n">
-        <v>7198853</v>
+        <v>7198926</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5494,7 +5480,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5504,7 +5490,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5524,17 +5510,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933207</v>
+        <v>128933146</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5542,21 +5528,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5570,10 +5556,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544978</v>
+        <v>545239</v>
       </c>
       <c r="R46" t="n">
-        <v>7198868</v>
+        <v>7198695</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5600,22 +5586,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Stående brandstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5642,32 +5633,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128934028</v>
+        <v>128933931</v>
       </c>
       <c r="B47" t="n">
-        <v>92145</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5677,13 +5668,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544728</v>
+        <v>545235</v>
       </c>
       <c r="R47" t="n">
-        <v>7198999</v>
+        <v>7198698</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5707,27 +5698,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5st fruktkroppar på gammal sälg</t>
+          <t>På död stående kelo</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5747,10 +5738,349 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128933144</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>545205</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7198721</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128933199</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>544762</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7199027</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128934059</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>544753</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7199025</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gammla ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>David Kenger</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
